--- a/pettycash/templates/excel_templates/IAR_template.xlsx
+++ b/pettycash/templates/excel_templates/IAR_template.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\rpalv\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Programming\tesda_pcvms\pettycash\templates\excel_templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E48EE1B1-153D-4CFF-8C7E-027EEFE2E234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9F15EBB0-2BE3-4B15-9006-B62DD3FB621F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -77,13 +77,7 @@
     <t xml:space="preserve">                Inspected, verified and found in        order as to quantity and specifications</t>
   </si>
   <si>
-    <t xml:space="preserve">Complete </t>
-  </si>
-  <si>
     <t>Inspection Officer/Inspection Committee</t>
-  </si>
-  <si>
-    <t xml:space="preserve">           Partial (pls. specify quantity)</t>
   </si>
   <si>
     <t>Supply Officer Designate</t>
@@ -93,6 +87,12 @@
   </si>
   <si>
     <t xml:space="preserve"> Requisitioning Office/Dept. : </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                      Complete </t>
+  </si>
+  <si>
+    <t xml:space="preserve">                      Partial (pls. specify quantity)</t>
   </si>
 </sst>
 </file>
@@ -584,7 +584,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="90">
+  <cellXfs count="91">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
@@ -707,34 +707,39 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -743,56 +748,58 @@
     <xf numFmtId="43" fontId="9" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="43" fontId="9" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="15" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -878,9 +885,9 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>400050</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>114300</xdr:rowOff>
+      <xdr:rowOff>114299</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="381000" cy="209550"/>
+    <xdr:ext cx="381000" cy="295275"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="6" name="Shape 6">
@@ -894,8 +901,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5160263" y="3679988"/>
-          <a:ext cx="371475" cy="200025"/>
+          <a:off x="3524250" y="4629149"/>
+          <a:ext cx="381000" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -914,12 +921,12 @@
         </a:ln>
       </xdr:spPr>
       <xdr:txBody>
-        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="t" anchorCtr="0">
+        <a:bodyPr spcFirstLastPara="1" wrap="square" lIns="91425" tIns="45700" rIns="91425" bIns="45700" anchor="ctr" anchorCtr="0">
           <a:noAutofit/>
         </a:bodyPr>
         <a:lstStyle/>
         <a:p>
-          <a:pPr marL="0" lvl="0" indent="0" algn="l" rtl="0">
+          <a:pPr marL="0" lvl="0" indent="0" algn="ctr" rtl="0">
             <a:spcBef>
               <a:spcPts val="0"/>
             </a:spcBef>
@@ -1012,9 +1019,9 @@
       <xdr:col>0</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>85726</xdr:rowOff>
     </xdr:from>
-    <xdr:ext cx="361950" cy="200025"/>
+    <xdr:ext cx="361950" cy="247650"/>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="8" name="Shape 8">
@@ -1028,8 +1035,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5169788" y="3684750"/>
-          <a:ext cx="352425" cy="190500"/>
+          <a:off x="47625" y="4600576"/>
+          <a:ext cx="361950" cy="247650"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1304,10 +1311,10 @@
       <c r="A1" s="9"/>
       <c r="B1" s="10"/>
       <c r="C1" s="10"/>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="80" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="57"/>
+      <c r="E1" s="81"/>
       <c r="F1" s="11"/>
       <c r="G1" s="11"/>
       <c r="H1" s="11"/>
@@ -1359,13 +1366,13 @@
       <c r="Z2" s="11"/>
     </row>
     <row r="3" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="82" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="53"/>
-      <c r="C3" s="53"/>
-      <c r="D3" s="53"/>
-      <c r="E3" s="56"/>
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="59"/>
       <c r="F3" s="11"/>
       <c r="G3" s="11"/>
       <c r="H3" s="11"/>
@@ -1390,8 +1397,8 @@
     </row>
     <row r="4" spans="1:26" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="15"/>
-      <c r="B4" s="63"/>
-      <c r="C4" s="53"/>
+      <c r="B4" s="83"/>
+      <c r="C4" s="58"/>
       <c r="D4" s="16"/>
       <c r="E4" s="17"/>
       <c r="F4" s="11"/>
@@ -1417,11 +1424,11 @@
       <c r="Z4" s="11"/>
     </row>
     <row r="5" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="89" t="s">
-        <v>22</v>
+      <c r="A5" s="51" t="s">
+        <v>20</v>
       </c>
-      <c r="B5" s="85"/>
-      <c r="C5" s="85"/>
+      <c r="B5" s="54"/>
+      <c r="C5" s="54"/>
       <c r="D5" s="18" t="s">
         <v>4</v>
       </c>
@@ -1450,8 +1457,8 @@
     </row>
     <row r="6" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
-      <c r="B6" s="64"/>
-      <c r="C6" s="51"/>
+      <c r="B6" s="84"/>
+      <c r="C6" s="85"/>
       <c r="D6" s="3"/>
       <c r="E6" s="20"/>
       <c r="F6" s="11"/>
@@ -1477,11 +1484,11 @@
       <c r="Z6" s="11"/>
     </row>
     <row r="7" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="82" t="s">
+      <c r="A7" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="83"/>
-      <c r="C7" s="83"/>
+      <c r="B7" s="79"/>
+      <c r="C7" s="79"/>
       <c r="D7" s="21" t="s">
         <v>6</v>
       </c>
@@ -1509,11 +1516,11 @@
       <c r="Z7" s="11"/>
     </row>
     <row r="8" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="84" t="s">
+      <c r="A8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="86"/>
-      <c r="C8" s="86"/>
+      <c r="B8" s="78"/>
+      <c r="C8" s="78"/>
       <c r="D8" s="6"/>
       <c r="E8" s="23"/>
       <c r="F8" s="11"/>
@@ -1539,11 +1546,11 @@
       <c r="Z8" s="11"/>
     </row>
     <row r="9" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="66" t="s">
-        <v>23</v>
+      <c r="A9" s="76" t="s">
+        <v>21</v>
       </c>
-      <c r="B9" s="53"/>
-      <c r="C9" s="54"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="77"/>
       <c r="D9" s="24" t="s">
         <v>8</v>
       </c>
@@ -1571,11 +1578,11 @@
       <c r="Z9" s="11"/>
     </row>
     <row r="10" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="66" t="s">
+      <c r="A10" s="76" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="53"/>
-      <c r="C10" s="54"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="77"/>
       <c r="D10" s="26" t="s">
         <v>10</v>
       </c>
@@ -1604,8 +1611,8 @@
     </row>
     <row r="11" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="54"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="77"/>
       <c r="D11" s="28"/>
       <c r="E11" s="2"/>
       <c r="F11" s="11"/>
@@ -1634,10 +1641,10 @@
       <c r="A12" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="B12" s="67" t="s">
+      <c r="B12" s="66" t="s">
         <v>12</v>
       </c>
-      <c r="C12" s="68"/>
+      <c r="C12" s="67"/>
       <c r="D12" s="30" t="s">
         <v>0</v>
       </c>
@@ -1668,8 +1675,8 @@
     </row>
     <row r="13" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A13" s="32"/>
-      <c r="B13" s="69"/>
-      <c r="C13" s="52"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="69"/>
       <c r="D13" s="33"/>
       <c r="E13" s="34"/>
       <c r="F13" s="35"/>
@@ -1697,7 +1704,7 @@
     <row r="14" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="32"/>
       <c r="B14" s="70"/>
-      <c r="C14" s="50"/>
+      <c r="C14" s="71"/>
       <c r="D14" s="33"/>
       <c r="E14" s="34"/>
       <c r="F14" s="11"/>
@@ -1725,7 +1732,7 @@
     <row r="15" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="32"/>
       <c r="B15" s="70"/>
-      <c r="C15" s="50"/>
+      <c r="C15" s="71"/>
       <c r="D15" s="33"/>
       <c r="E15" s="34"/>
       <c r="F15" s="11"/>
@@ -1753,7 +1760,7 @@
     <row r="16" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="32"/>
       <c r="B16" s="70"/>
-      <c r="C16" s="50"/>
+      <c r="C16" s="71"/>
       <c r="D16" s="33"/>
       <c r="E16" s="34"/>
       <c r="F16" s="11"/>
@@ -1781,7 +1788,7 @@
     <row r="17" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="32"/>
       <c r="B17" s="70"/>
-      <c r="C17" s="50"/>
+      <c r="C17" s="71"/>
       <c r="D17" s="33"/>
       <c r="E17" s="34"/>
       <c r="F17" s="11"/>
@@ -1809,7 +1816,7 @@
     <row r="18" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="32"/>
       <c r="B18" s="70"/>
-      <c r="C18" s="50"/>
+      <c r="C18" s="71"/>
       <c r="D18" s="33"/>
       <c r="E18" s="34"/>
       <c r="F18" s="11"/>
@@ -1837,7 +1844,7 @@
     <row r="19" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="32"/>
       <c r="B19" s="70"/>
-      <c r="C19" s="50"/>
+      <c r="C19" s="71"/>
       <c r="D19" s="33"/>
       <c r="E19" s="34"/>
       <c r="F19" s="11"/>
@@ -1865,7 +1872,7 @@
     <row r="20" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="32"/>
       <c r="B20" s="70"/>
-      <c r="C20" s="50"/>
+      <c r="C20" s="71"/>
       <c r="D20" s="33"/>
       <c r="E20" s="34"/>
       <c r="F20" s="11"/>
@@ -1893,7 +1900,7 @@
     <row r="21" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A21" s="32"/>
       <c r="B21" s="70"/>
-      <c r="C21" s="50"/>
+      <c r="C21" s="71"/>
       <c r="D21" s="33"/>
       <c r="E21" s="34"/>
       <c r="F21" s="11"/>
@@ -1919,15 +1926,15 @@
       <c r="Z21" s="11"/>
     </row>
     <row r="22" spans="1:26" ht="16.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="71" t="s">
+      <c r="A22" s="72" t="s">
         <v>13</v>
       </c>
-      <c r="B22" s="60"/>
-      <c r="C22" s="81" t="s">
+      <c r="B22" s="73"/>
+      <c r="C22" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="D22" s="59"/>
-      <c r="E22" s="58"/>
+      <c r="D22" s="75"/>
+      <c r="E22" s="56"/>
     </row>
     <row r="23" spans="1:26" ht="24" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A23" s="37" t="s">
@@ -1937,26 +1944,26 @@
       <c r="C23" s="39" t="s">
         <v>16</v>
       </c>
-      <c r="D23" s="87"/>
-      <c r="E23" s="88"/>
+      <c r="D23" s="52"/>
+      <c r="E23" s="53"/>
     </row>
     <row r="24" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A24" s="72" t="s">
+      <c r="A24" s="62" t="s">
         <v>17</v>
       </c>
-      <c r="B24" s="73"/>
-      <c r="C24" s="78" t="s">
-        <v>18</v>
+      <c r="B24" s="57"/>
+      <c r="C24" s="86" t="s">
+        <v>22</v>
       </c>
-      <c r="D24" s="65"/>
-      <c r="E24" s="73"/>
+      <c r="D24" s="87"/>
+      <c r="E24" s="88"/>
     </row>
     <row r="25" spans="1:26" ht="12.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="74"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="53"/>
-      <c r="D25" s="53"/>
-      <c r="E25" s="56"/>
+      <c r="A25" s="63"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="78"/>
+      <c r="D25" s="78"/>
+      <c r="E25" s="89"/>
     </row>
     <row r="26" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="7"/>
@@ -1966,15 +1973,15 @@
       <c r="E26" s="42"/>
     </row>
     <row r="27" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A27" s="75" t="s">
-        <v>19</v>
+      <c r="A27" s="64" t="s">
+        <v>18</v>
       </c>
-      <c r="B27" s="56"/>
-      <c r="C27" s="79" t="s">
-        <v>20</v>
+      <c r="B27" s="59"/>
+      <c r="C27" s="90" t="s">
+        <v>23</v>
       </c>
-      <c r="D27" s="53"/>
-      <c r="E27" s="56"/>
+      <c r="D27" s="78"/>
+      <c r="E27" s="89"/>
     </row>
     <row r="28" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A28" s="12"/>
@@ -1991,20 +1998,20 @@
       <c r="E29" s="40"/>
     </row>
     <row r="30" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="76"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="80"/>
-      <c r="D30" s="53"/>
-      <c r="E30" s="56"/>
+      <c r="A30" s="65"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="59"/>
     </row>
     <row r="31" spans="1:26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="77"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="55" t="s">
-        <v>21</v>
+      <c r="A31" s="55"/>
+      <c r="B31" s="56"/>
+      <c r="C31" s="61" t="s">
+        <v>19</v>
       </c>
-      <c r="D31" s="53"/>
-      <c r="E31" s="56"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="59"/>
     </row>
     <row r="32" spans="1:26" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="44"/>
@@ -2021,15 +2028,15 @@
       <c r="E33" s="4"/>
     </row>
     <row r="34" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A34" s="76"/>
-      <c r="B34" s="56"/>
+      <c r="A34" s="65"/>
+      <c r="B34" s="59"/>
       <c r="C34" s="46"/>
       <c r="D34" s="46"/>
       <c r="E34" s="47"/>
     </row>
     <row r="35" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A35" s="77"/>
-      <c r="B35" s="58"/>
+      <c r="A35" s="55"/>
+      <c r="B35" s="56"/>
       <c r="C35" s="48"/>
       <c r="D35" s="48"/>
       <c r="E35" s="49"/>
@@ -3001,6 +3008,23 @@
     <row r="1000" ht="12.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="33">
+    <mergeCell ref="D1:E1"/>
+    <mergeCell ref="A3:E3"/>
+    <mergeCell ref="B4:C4"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="A9:C9"/>
+    <mergeCell ref="A10:C10"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="C22:E22"/>
     <mergeCell ref="D23:E23"/>
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="A35:B35"/>
@@ -3017,23 +3041,6 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="B21:C21"/>
-    <mergeCell ref="C22:E22"/>
-    <mergeCell ref="A9:C9"/>
-    <mergeCell ref="A10:C10"/>
-    <mergeCell ref="B11:C11"/>
-    <mergeCell ref="B8:C8"/>
-    <mergeCell ref="B7:C7"/>
-    <mergeCell ref="D1:E1"/>
-    <mergeCell ref="A3:E3"/>
-    <mergeCell ref="B4:C4"/>
-    <mergeCell ref="B6:C6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="portrait"/>
